--- a/precios_base.xlsx
+++ b/precios_base.xlsx
@@ -70,7 +70,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="12.0"/>
       <color theme="1"/>
@@ -80,15 +80,12 @@
     <font>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -105,21 +102,15 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="bottom"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -375,7 +366,6 @@
       <c r="E2" s="2">
         <v>21.0</v>
       </c>
-      <c r="G2" s="4"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
@@ -395,7 +385,6 @@
       <c r="E3" s="2">
         <v>37.5</v>
       </c>
-      <c r="G3" s="4"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
     </row>
@@ -415,7 +404,6 @@
       <c r="E4" s="2">
         <v>50.0</v>
       </c>
-      <c r="G4" s="4"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
     </row>
@@ -435,7 +423,6 @@
       <c r="E5" s="2">
         <v>21.5</v>
       </c>
-      <c r="G5" s="4"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
     </row>
@@ -455,7 +442,6 @@
       <c r="E6" s="2">
         <v>39.0</v>
       </c>
-      <c r="G6" s="4"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
     </row>
@@ -475,7 +461,6 @@
       <c r="E7" s="2">
         <v>52.0</v>
       </c>
-      <c r="G7" s="4"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
     </row>
@@ -495,7 +480,6 @@
       <c r="E8" s="2">
         <v>22.0</v>
       </c>
-      <c r="G8" s="4"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
@@ -515,7 +499,6 @@
       <c r="E9" s="2">
         <v>39.5</v>
       </c>
-      <c r="G9" s="4"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
@@ -535,7 +518,6 @@
       <c r="E10" s="2">
         <v>53.0</v>
       </c>
-      <c r="G10" s="4"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
@@ -555,7 +537,6 @@
       <c r="E11" s="2">
         <v>22.5</v>
       </c>
-      <c r="G11" s="4"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
     </row>
@@ -575,7 +556,6 @@
       <c r="E12" s="2">
         <v>40.0</v>
       </c>
-      <c r="G12" s="4"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
     </row>
@@ -595,7 +575,6 @@
       <c r="E13" s="2">
         <v>53.5</v>
       </c>
-      <c r="G13" s="4"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
     </row>
@@ -615,7 +594,6 @@
       <c r="E14" s="2">
         <v>23.0</v>
       </c>
-      <c r="G14" s="4"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
     </row>
@@ -635,7 +613,6 @@
       <c r="E15" s="2">
         <v>41.0</v>
       </c>
-      <c r="G15" s="4"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
     </row>
@@ -655,7 +632,6 @@
       <c r="E16" s="2">
         <v>54.0</v>
       </c>
-      <c r="G16" s="4"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
     </row>
@@ -675,7 +651,6 @@
       <c r="E17" s="2">
         <v>23.5</v>
       </c>
-      <c r="G17" s="4"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
     </row>
@@ -695,7 +670,6 @@
       <c r="E18" s="2">
         <v>41.5</v>
       </c>
-      <c r="G18" s="4"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
     </row>
@@ -712,10 +686,9 @@
       <c r="D19" s="3">
         <v>6.0</v>
       </c>
-      <c r="E19" s="5">
-        <v>54.5</v>
-      </c>
-      <c r="G19" s="4"/>
+      <c r="E19" s="2">
+        <v>45.0</v>
+      </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
     </row>
@@ -735,7 +708,6 @@
       <c r="E20" s="2">
         <v>38.0</v>
       </c>
-      <c r="G20" s="4"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
     </row>
@@ -755,7 +727,6 @@
       <c r="E21" s="2">
         <v>50.0</v>
       </c>
-      <c r="G21" s="4"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
     </row>
@@ -775,7 +746,6 @@
       <c r="E22" s="2">
         <v>61.5</v>
       </c>
-      <c r="G22" s="4"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
     </row>
@@ -795,7 +765,6 @@
       <c r="E23" s="2">
         <v>94.0</v>
       </c>
-      <c r="G23" s="4"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
     </row>
@@ -815,7 +784,6 @@
       <c r="E24" s="2">
         <v>117.0</v>
       </c>
-      <c r="G24" s="4"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
     </row>
@@ -835,7 +803,6 @@
       <c r="E25" s="2">
         <v>156.0</v>
       </c>
-      <c r="G25" s="4"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
     </row>
@@ -855,7 +822,6 @@
       <c r="E26" s="2">
         <v>168.0</v>
       </c>
-      <c r="G26" s="4"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
     </row>
@@ -875,7 +841,6 @@
       <c r="E27" s="2">
         <v>39.0</v>
       </c>
-      <c r="G27" s="4"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
     </row>
@@ -895,7 +860,6 @@
       <c r="E28" s="2">
         <v>50.5</v>
       </c>
-      <c r="G28" s="4"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
     </row>
@@ -915,7 +879,6 @@
       <c r="E29" s="2">
         <v>62.0</v>
       </c>
-      <c r="G29" s="4"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
     </row>
@@ -935,7 +898,6 @@
       <c r="E30" s="2">
         <v>95.0</v>
       </c>
-      <c r="G30" s="4"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
     </row>
@@ -955,7 +917,6 @@
       <c r="E31" s="2">
         <v>121.0</v>
       </c>
-      <c r="G31" s="4"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
     </row>
@@ -975,7 +936,6 @@
       <c r="E32" s="2">
         <v>163.0</v>
       </c>
-      <c r="G32" s="4"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
     </row>
@@ -995,7 +955,6 @@
       <c r="E33" s="2">
         <v>176.0</v>
       </c>
-      <c r="G33" s="4"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
     </row>
@@ -1015,7 +974,6 @@
       <c r="E34" s="2">
         <v>39.5</v>
       </c>
-      <c r="G34" s="4"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
     </row>
@@ -1035,7 +993,6 @@
       <c r="E35" s="2">
         <v>51.0</v>
       </c>
-      <c r="G35" s="4"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
     </row>
@@ -1055,7 +1012,6 @@
       <c r="E36" s="2">
         <v>63.0</v>
       </c>
-      <c r="G36" s="4"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
     </row>
@@ -1075,7 +1031,6 @@
       <c r="E37" s="2">
         <v>96.5</v>
       </c>
-      <c r="G37" s="4"/>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
     </row>
@@ -1095,7 +1050,6 @@
       <c r="E38" s="2">
         <v>124.0</v>
       </c>
-      <c r="G38" s="4"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
     </row>
@@ -1115,7 +1069,6 @@
       <c r="E39" s="2">
         <v>167.0</v>
       </c>
-      <c r="G39" s="4"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
     </row>
@@ -1135,7 +1088,6 @@
       <c r="E40" s="2">
         <v>179.0</v>
       </c>
-      <c r="G40" s="4"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
     </row>
@@ -1155,7 +1107,6 @@
       <c r="E41" s="2">
         <v>40.0</v>
       </c>
-      <c r="G41" s="4"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
     </row>
@@ -1175,7 +1126,6 @@
       <c r="E42" s="2">
         <v>52.0</v>
       </c>
-      <c r="G42" s="4"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
     </row>
@@ -1195,7 +1145,6 @@
       <c r="E43" s="2">
         <v>64.0</v>
       </c>
-      <c r="G43" s="4"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
     </row>
@@ -1215,7 +1164,6 @@
       <c r="E44" s="2">
         <v>99.0</v>
       </c>
-      <c r="G44" s="4"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
     </row>
@@ -1235,7 +1183,6 @@
       <c r="E45" s="2">
         <v>125.5</v>
       </c>
-      <c r="G45" s="4"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
     </row>
@@ -1255,7 +1202,6 @@
       <c r="E46" s="2">
         <v>167.5</v>
       </c>
-      <c r="G46" s="4"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
     </row>
@@ -1275,7 +1221,6 @@
       <c r="E47" s="2">
         <v>180.0</v>
       </c>
-      <c r="G47" s="4"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
     </row>
@@ -1295,7 +1240,6 @@
       <c r="E48" s="2">
         <v>41.0</v>
       </c>
-      <c r="G48" s="4"/>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
     </row>
@@ -1315,7 +1259,6 @@
       <c r="E49" s="2">
         <v>53.5</v>
       </c>
-      <c r="G49" s="4"/>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
     </row>
@@ -1335,7 +1278,6 @@
       <c r="E50" s="2">
         <v>66.0</v>
       </c>
-      <c r="G50" s="4"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
     </row>
@@ -1355,7 +1297,6 @@
       <c r="E51" s="2">
         <v>101.0</v>
       </c>
-      <c r="G51" s="4"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
     </row>
@@ -1375,7 +1316,6 @@
       <c r="E52" s="2">
         <v>126.0</v>
       </c>
-      <c r="G52" s="4"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
     </row>
@@ -1395,7 +1335,6 @@
       <c r="E53" s="2">
         <v>168.0</v>
       </c>
-      <c r="G53" s="4"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
     </row>
@@ -1415,7 +1354,6 @@
       <c r="E54" s="2">
         <v>181.0</v>
       </c>
-      <c r="G54" s="4"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
     </row>
@@ -1435,7 +1373,6 @@
       <c r="E55" s="2">
         <v>42.5</v>
       </c>
-      <c r="G55" s="4"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
     </row>
@@ -1455,7 +1392,6 @@
       <c r="E56" s="2">
         <v>54.0</v>
       </c>
-      <c r="G56" s="4"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
     </row>
@@ -1475,7 +1411,6 @@
       <c r="E57" s="2">
         <v>66.5</v>
       </c>
-      <c r="G57" s="4"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
     </row>
@@ -1495,7 +1430,6 @@
       <c r="E58" s="2">
         <v>103.0</v>
       </c>
-      <c r="G58" s="4"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
     </row>
@@ -1515,7 +1449,6 @@
       <c r="E59" s="2">
         <v>127.0</v>
       </c>
-      <c r="G59" s="4"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
     </row>
@@ -1535,7 +1468,6 @@
       <c r="E60" s="2">
         <v>169.0</v>
       </c>
-      <c r="G60" s="4"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
     </row>
@@ -1555,7 +1487,6 @@
       <c r="E61" s="2">
         <v>182.0</v>
       </c>
-      <c r="G61" s="4"/>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
     </row>
@@ -1575,7 +1506,6 @@
       <c r="E62" s="2">
         <v>48.5</v>
       </c>
-      <c r="G62" s="4"/>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
     </row>
@@ -1595,7 +1525,6 @@
       <c r="E63" s="2">
         <v>59.5</v>
       </c>
-      <c r="G63" s="4"/>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
     </row>
@@ -1615,7 +1544,6 @@
       <c r="E64" s="2">
         <v>72.5</v>
       </c>
-      <c r="G64" s="4"/>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
     </row>
@@ -1635,7 +1563,6 @@
       <c r="E65" s="2">
         <v>110.0</v>
       </c>
-      <c r="G65" s="4"/>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
     </row>
@@ -1655,7 +1582,6 @@
       <c r="E66" s="2">
         <v>132.0</v>
       </c>
-      <c r="G66" s="4"/>
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
     </row>
@@ -1675,7 +1601,6 @@
       <c r="E67" s="2">
         <v>196.0</v>
       </c>
-      <c r="G67" s="4"/>
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
     </row>
@@ -1695,7 +1620,6 @@
       <c r="E68" s="2">
         <v>49.0</v>
       </c>
-      <c r="G68" s="4"/>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
     </row>
@@ -1715,7 +1639,6 @@
       <c r="E69" s="2">
         <v>61.0</v>
       </c>
-      <c r="G69" s="4"/>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
     </row>
@@ -1735,7 +1658,6 @@
       <c r="E70" s="2">
         <v>73.5</v>
       </c>
-      <c r="G70" s="4"/>
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
     </row>
@@ -1755,7 +1677,6 @@
       <c r="E71" s="2">
         <v>112.0</v>
       </c>
-      <c r="G71" s="4"/>
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
     </row>
@@ -1775,7 +1696,6 @@
       <c r="E72" s="2">
         <v>133.0</v>
       </c>
-      <c r="G72" s="4"/>
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
     </row>
@@ -1795,7 +1715,6 @@
       <c r="E73" s="2">
         <v>201.0</v>
       </c>
-      <c r="G73" s="4"/>
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
     </row>
@@ -1815,7 +1734,6 @@
       <c r="E74" s="2">
         <v>50.0</v>
       </c>
-      <c r="G74" s="4"/>
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
     </row>
@@ -1835,7 +1753,6 @@
       <c r="E75" s="2">
         <v>62.0</v>
       </c>
-      <c r="G75" s="4"/>
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
     </row>
@@ -1855,7 +1772,6 @@
       <c r="E76" s="2">
         <v>75.0</v>
       </c>
-      <c r="G76" s="4"/>
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
     </row>
@@ -1875,7 +1791,6 @@
       <c r="E77" s="2">
         <v>114.0</v>
       </c>
-      <c r="G77" s="4"/>
       <c r="I77" s="2"/>
       <c r="J77" s="2"/>
     </row>
@@ -1895,7 +1810,6 @@
       <c r="E78" s="2">
         <v>137.0</v>
       </c>
-      <c r="G78" s="4"/>
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
     </row>
@@ -1915,7 +1829,6 @@
       <c r="E79" s="2">
         <v>210.0</v>
       </c>
-      <c r="G79" s="4"/>
       <c r="I79" s="2"/>
       <c r="J79" s="2"/>
     </row>
@@ -1935,7 +1848,6 @@
       <c r="E80" s="2">
         <v>50.5</v>
       </c>
-      <c r="G80" s="4"/>
       <c r="I80" s="2"/>
       <c r="J80" s="2"/>
     </row>
@@ -1955,7 +1867,6 @@
       <c r="E81" s="2">
         <v>62.5</v>
       </c>
-      <c r="G81" s="4"/>
       <c r="I81" s="2"/>
       <c r="J81" s="2"/>
     </row>
@@ -1975,7 +1886,6 @@
       <c r="E82" s="2">
         <v>75.5</v>
       </c>
-      <c r="G82" s="4"/>
       <c r="I82" s="2"/>
       <c r="J82" s="2"/>
     </row>
@@ -1995,7 +1905,6 @@
       <c r="E83" s="2">
         <v>114.5</v>
       </c>
-      <c r="G83" s="4"/>
       <c r="I83" s="2"/>
       <c r="J83" s="2"/>
     </row>
@@ -2015,7 +1924,6 @@
       <c r="E84" s="2">
         <v>137.5</v>
       </c>
-      <c r="G84" s="4"/>
       <c r="I84" s="2"/>
       <c r="J84" s="2"/>
     </row>
@@ -2035,7 +1943,6 @@
       <c r="E85" s="2">
         <v>210.5</v>
       </c>
-      <c r="G85" s="4"/>
       <c r="I85" s="2"/>
       <c r="J85" s="2"/>
     </row>
@@ -2055,7 +1962,6 @@
       <c r="E86" s="2">
         <v>52.0</v>
       </c>
-      <c r="G86" s="4"/>
       <c r="I86" s="2"/>
       <c r="J86" s="2"/>
     </row>
@@ -2075,7 +1981,6 @@
       <c r="E87" s="2">
         <v>63.0</v>
       </c>
-      <c r="G87" s="4"/>
       <c r="I87" s="2"/>
       <c r="J87" s="2"/>
     </row>
@@ -2095,7 +2000,6 @@
       <c r="E88" s="2">
         <v>77.0</v>
       </c>
-      <c r="G88" s="4"/>
       <c r="I88" s="2"/>
       <c r="J88" s="2"/>
     </row>
@@ -2115,7 +2019,6 @@
       <c r="E89" s="2">
         <v>115.0</v>
       </c>
-      <c r="G89" s="4"/>
       <c r="I89" s="2"/>
       <c r="J89" s="2"/>
     </row>
@@ -2135,7 +2038,6 @@
       <c r="E90" s="2">
         <v>140.0</v>
       </c>
-      <c r="G90" s="4"/>
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
     </row>
@@ -2155,7 +2057,6 @@
       <c r="E91" s="2">
         <v>230.0</v>
       </c>
-      <c r="G91" s="4"/>
       <c r="I91" s="2"/>
       <c r="J91" s="2"/>
     </row>
@@ -2175,7 +2076,6 @@
       <c r="E92" s="2">
         <v>53.0</v>
       </c>
-      <c r="G92" s="4"/>
       <c r="I92" s="2"/>
       <c r="J92" s="2"/>
     </row>
@@ -2195,7 +2095,6 @@
       <c r="E93" s="2">
         <v>65.0</v>
       </c>
-      <c r="G93" s="4"/>
       <c r="I93" s="2"/>
       <c r="J93" s="2"/>
     </row>
@@ -2215,7 +2114,6 @@
       <c r="E94" s="2">
         <v>78.5</v>
       </c>
-      <c r="G94" s="4"/>
       <c r="I94" s="2"/>
       <c r="J94" s="2"/>
     </row>
@@ -2235,7 +2133,6 @@
       <c r="E95" s="2">
         <v>118.0</v>
       </c>
-      <c r="G95" s="4"/>
       <c r="I95" s="2"/>
       <c r="J95" s="2"/>
     </row>
@@ -2255,7 +2152,6 @@
       <c r="E96" s="2">
         <v>142.0</v>
       </c>
-      <c r="G96" s="4"/>
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
     </row>
@@ -2275,7 +2171,6 @@
       <c r="E97" s="2">
         <v>235.0</v>
       </c>
-      <c r="G97" s="4"/>
       <c r="I97" s="2"/>
       <c r="J97" s="2"/>
     </row>
@@ -2295,7 +2190,6 @@
       <c r="E98" s="2">
         <v>50.0</v>
       </c>
-      <c r="G98" s="4"/>
       <c r="I98" s="2"/>
       <c r="J98" s="2"/>
     </row>
@@ -2315,7 +2209,6 @@
       <c r="E99" s="2">
         <v>60.0</v>
       </c>
-      <c r="G99" s="4"/>
       <c r="I99" s="2"/>
       <c r="J99" s="2"/>
     </row>
@@ -2335,7 +2228,6 @@
       <c r="E100" s="2">
         <v>72.0</v>
       </c>
-      <c r="G100" s="4"/>
       <c r="I100" s="2"/>
       <c r="J100" s="2"/>
     </row>
@@ -2355,7 +2247,6 @@
       <c r="E101" s="2">
         <v>105.0</v>
       </c>
-      <c r="G101" s="4"/>
       <c r="I101" s="2"/>
       <c r="J101" s="2"/>
     </row>
@@ -2375,7 +2266,6 @@
       <c r="E102" s="2">
         <v>128.0</v>
       </c>
-      <c r="G102" s="4"/>
       <c r="I102" s="2"/>
       <c r="J102" s="2"/>
     </row>
@@ -2395,7 +2285,6 @@
       <c r="E103" s="2">
         <v>166.0</v>
       </c>
-      <c r="G103" s="4"/>
       <c r="I103" s="2"/>
       <c r="J103" s="2"/>
     </row>
@@ -2415,7 +2304,6 @@
       <c r="E104" s="2">
         <v>225.0</v>
       </c>
-      <c r="G104" s="4"/>
       <c r="I104" s="2"/>
       <c r="J104" s="2"/>
     </row>
@@ -2435,7 +2323,6 @@
       <c r="E105" s="2">
         <v>51.0</v>
       </c>
-      <c r="G105" s="4"/>
       <c r="I105" s="2"/>
       <c r="J105" s="2"/>
     </row>
@@ -2455,7 +2342,6 @@
       <c r="E106" s="2">
         <v>62.0</v>
       </c>
-      <c r="G106" s="4"/>
       <c r="I106" s="2"/>
       <c r="J106" s="2"/>
     </row>
@@ -2475,7 +2361,6 @@
       <c r="E107" s="2">
         <v>73.0</v>
       </c>
-      <c r="G107" s="4"/>
       <c r="I107" s="2"/>
       <c r="J107" s="2"/>
     </row>
@@ -2495,7 +2380,6 @@
       <c r="E108" s="2">
         <v>107.0</v>
       </c>
-      <c r="G108" s="4"/>
       <c r="I108" s="2"/>
       <c r="J108" s="2"/>
     </row>
@@ -2515,7 +2399,6 @@
       <c r="E109" s="2">
         <v>130.0</v>
       </c>
-      <c r="G109" s="4"/>
       <c r="I109" s="2"/>
       <c r="J109" s="2"/>
     </row>
@@ -2535,7 +2418,6 @@
       <c r="E110" s="2">
         <v>167.0</v>
       </c>
-      <c r="G110" s="4"/>
       <c r="I110" s="2"/>
       <c r="J110" s="2"/>
     </row>
@@ -2555,7 +2437,6 @@
       <c r="E111" s="2">
         <v>227.0</v>
       </c>
-      <c r="G111" s="4"/>
       <c r="I111" s="2"/>
       <c r="J111" s="2"/>
     </row>
@@ -2575,7 +2456,6 @@
       <c r="E112" s="2">
         <v>52.0</v>
       </c>
-      <c r="G112" s="4"/>
       <c r="I112" s="2"/>
       <c r="J112" s="2"/>
     </row>
@@ -2595,7 +2475,6 @@
       <c r="E113" s="2">
         <v>63.0</v>
       </c>
-      <c r="G113" s="4"/>
       <c r="I113" s="2"/>
       <c r="J113" s="2"/>
     </row>
@@ -2615,7 +2494,6 @@
       <c r="E114" s="2">
         <v>74.0</v>
       </c>
-      <c r="G114" s="4"/>
       <c r="I114" s="2"/>
       <c r="J114" s="2"/>
     </row>
@@ -2635,7 +2513,6 @@
       <c r="E115" s="2">
         <v>109.0</v>
       </c>
-      <c r="G115" s="4"/>
       <c r="I115" s="2"/>
       <c r="J115" s="2"/>
     </row>
@@ -2655,7 +2532,6 @@
       <c r="E116" s="2">
         <v>131.0</v>
       </c>
-      <c r="G116" s="4"/>
       <c r="I116" s="2"/>
       <c r="J116" s="2"/>
     </row>
@@ -2675,7 +2551,6 @@
       <c r="E117" s="2">
         <v>169.0</v>
       </c>
-      <c r="G117" s="4"/>
       <c r="I117" s="2"/>
       <c r="J117" s="2"/>
     </row>
@@ -2695,7 +2570,6 @@
       <c r="E118" s="2">
         <v>229.0</v>
       </c>
-      <c r="G118" s="4"/>
       <c r="I118" s="2"/>
       <c r="J118" s="2"/>
     </row>
@@ -2715,7 +2589,6 @@
       <c r="E119" s="2">
         <v>53.0</v>
       </c>
-      <c r="G119" s="4"/>
       <c r="I119" s="2"/>
       <c r="J119" s="2"/>
     </row>
@@ -2735,7 +2608,6 @@
       <c r="E120" s="2">
         <v>64.0</v>
       </c>
-      <c r="G120" s="4"/>
       <c r="I120" s="2"/>
       <c r="J120" s="2"/>
     </row>
@@ -2755,7 +2627,6 @@
       <c r="E121" s="2">
         <v>75.0</v>
       </c>
-      <c r="G121" s="4"/>
       <c r="I121" s="2"/>
       <c r="J121" s="2"/>
     </row>
@@ -2775,7 +2646,6 @@
       <c r="E122" s="2">
         <v>110.0</v>
       </c>
-      <c r="G122" s="4"/>
       <c r="I122" s="2"/>
       <c r="J122" s="2"/>
     </row>
@@ -2795,7 +2665,6 @@
       <c r="E123" s="2">
         <v>135.0</v>
       </c>
-      <c r="G123" s="4"/>
       <c r="I123" s="2"/>
       <c r="J123" s="2"/>
     </row>
@@ -2815,7 +2684,6 @@
       <c r="E124" s="2">
         <v>172.0</v>
       </c>
-      <c r="G124" s="4"/>
       <c r="I124" s="2"/>
       <c r="J124" s="2"/>
     </row>
@@ -2835,7 +2703,6 @@
       <c r="E125" s="2">
         <v>235.0</v>
       </c>
-      <c r="G125" s="4"/>
       <c r="I125" s="2"/>
       <c r="J125" s="2"/>
     </row>
@@ -2855,7 +2722,6 @@
       <c r="E126" s="2">
         <v>54.0</v>
       </c>
-      <c r="G126" s="4"/>
       <c r="I126" s="2"/>
       <c r="J126" s="2"/>
     </row>
@@ -2875,7 +2741,6 @@
       <c r="E127" s="2">
         <v>65.0</v>
       </c>
-      <c r="G127" s="4"/>
       <c r="I127" s="2"/>
       <c r="J127" s="2"/>
     </row>
@@ -2895,7 +2760,6 @@
       <c r="E128" s="2">
         <v>78.0</v>
       </c>
-      <c r="G128" s="4"/>
       <c r="I128" s="2"/>
       <c r="J128" s="2"/>
     </row>
@@ -2915,7 +2779,6 @@
       <c r="E129" s="2">
         <v>112.0</v>
       </c>
-      <c r="G129" s="4"/>
       <c r="I129" s="2"/>
       <c r="J129" s="2"/>
     </row>
@@ -2935,7 +2798,6 @@
       <c r="E130" s="2">
         <v>139.0</v>
       </c>
-      <c r="G130" s="4"/>
       <c r="I130" s="2"/>
       <c r="J130" s="2"/>
     </row>
@@ -2955,7 +2817,6 @@
       <c r="E131" s="2">
         <v>175.0</v>
       </c>
-      <c r="G131" s="4"/>
       <c r="I131" s="2"/>
       <c r="J131" s="2"/>
     </row>
@@ -2975,7 +2836,6 @@
       <c r="E132" s="2">
         <v>239.0</v>
       </c>
-      <c r="G132" s="4"/>
       <c r="I132" s="2"/>
       <c r="J132" s="2"/>
     </row>
@@ -2995,7 +2855,6 @@
       <c r="E133" s="2">
         <v>55.0</v>
       </c>
-      <c r="G133" s="4"/>
       <c r="I133" s="2"/>
       <c r="J133" s="2"/>
     </row>
@@ -3015,7 +2874,6 @@
       <c r="E134" s="2">
         <v>66.0</v>
       </c>
-      <c r="G134" s="4"/>
       <c r="I134" s="2"/>
       <c r="J134" s="2"/>
     </row>
@@ -3035,7 +2893,6 @@
       <c r="E135" s="2">
         <v>79.0</v>
       </c>
-      <c r="G135" s="4"/>
       <c r="I135" s="2"/>
       <c r="J135" s="2"/>
     </row>
@@ -3055,7 +2912,6 @@
       <c r="E136" s="2">
         <v>114.0</v>
       </c>
-      <c r="G136" s="4"/>
       <c r="I136" s="2"/>
       <c r="J136" s="2"/>
     </row>
@@ -3075,7 +2931,6 @@
       <c r="E137" s="2">
         <v>140.0</v>
       </c>
-      <c r="G137" s="4"/>
       <c r="I137" s="2"/>
       <c r="J137" s="2"/>
     </row>
@@ -3095,7 +2950,6 @@
       <c r="E138" s="2">
         <v>179.0</v>
       </c>
-      <c r="G138" s="4"/>
       <c r="I138" s="2"/>
       <c r="J138" s="2"/>
     </row>
@@ -3115,7 +2969,6 @@
       <c r="E139" s="2">
         <v>240.0</v>
       </c>
-      <c r="G139" s="4"/>
       <c r="I139" s="2"/>
       <c r="J139" s="2"/>
     </row>
@@ -3135,7 +2988,6 @@
       <c r="E140" s="2">
         <v>62.0</v>
       </c>
-      <c r="G140" s="4"/>
       <c r="I140" s="2"/>
       <c r="J140" s="2"/>
     </row>
@@ -3155,7 +3007,6 @@
       <c r="E141" s="2">
         <v>72.0</v>
       </c>
-      <c r="G141" s="4"/>
       <c r="I141" s="2"/>
       <c r="J141" s="2"/>
     </row>
@@ -3175,7 +3026,6 @@
       <c r="E142" s="2">
         <v>92.0</v>
       </c>
-      <c r="G142" s="4"/>
       <c r="I142" s="2"/>
       <c r="J142" s="2"/>
     </row>
@@ -3195,7 +3045,6 @@
       <c r="E143" s="2">
         <v>149.0</v>
       </c>
-      <c r="G143" s="4"/>
       <c r="I143" s="2"/>
       <c r="J143" s="2"/>
     </row>
@@ -3215,7 +3064,6 @@
       <c r="E144" s="2">
         <v>175.0</v>
       </c>
-      <c r="G144" s="4"/>
       <c r="I144" s="2"/>
       <c r="J144" s="2"/>
     </row>
@@ -3235,7 +3083,6 @@
       <c r="E145" s="2">
         <v>239.0</v>
       </c>
-      <c r="G145" s="4"/>
       <c r="I145" s="2"/>
       <c r="J145" s="2"/>
     </row>
@@ -3255,7 +3102,6 @@
       <c r="E146" s="2">
         <v>255.0</v>
       </c>
-      <c r="G146" s="4"/>
       <c r="I146" s="2"/>
       <c r="J146" s="2"/>
     </row>
@@ -3275,7 +3121,6 @@
       <c r="E147" s="2">
         <v>64.0</v>
       </c>
-      <c r="G147" s="4"/>
       <c r="I147" s="2"/>
       <c r="J147" s="2"/>
     </row>
@@ -3295,7 +3140,6 @@
       <c r="E148" s="2">
         <v>75.0</v>
       </c>
-      <c r="G148" s="4"/>
       <c r="I148" s="2"/>
       <c r="J148" s="2"/>
     </row>
@@ -3315,7 +3159,6 @@
       <c r="E149" s="2">
         <v>94.0</v>
       </c>
-      <c r="G149" s="4"/>
       <c r="I149" s="2"/>
       <c r="J149" s="2"/>
     </row>
@@ -3335,7 +3178,6 @@
       <c r="E150" s="2">
         <v>155.0</v>
       </c>
-      <c r="G150" s="4"/>
       <c r="I150" s="2"/>
       <c r="J150" s="2"/>
     </row>
@@ -3355,7 +3197,6 @@
       <c r="E151" s="2">
         <v>181.0</v>
       </c>
-      <c r="G151" s="4"/>
       <c r="I151" s="2"/>
       <c r="J151" s="2"/>
     </row>
@@ -3375,7 +3216,6 @@
       <c r="E152" s="2">
         <v>255.0</v>
       </c>
-      <c r="G152" s="4"/>
       <c r="I152" s="2"/>
       <c r="J152" s="2"/>
     </row>
@@ -3395,7 +3235,6 @@
       <c r="E153" s="2">
         <v>259.0</v>
       </c>
-      <c r="G153" s="4"/>
       <c r="I153" s="2"/>
       <c r="J153" s="2"/>
     </row>
@@ -3415,7 +3254,6 @@
       <c r="E154" s="2">
         <v>64.0</v>
       </c>
-      <c r="G154" s="4"/>
       <c r="I154" s="2"/>
       <c r="J154" s="2"/>
     </row>
@@ -3435,7 +3273,6 @@
       <c r="E155" s="2">
         <v>76.0</v>
       </c>
-      <c r="G155" s="4"/>
       <c r="I155" s="2"/>
       <c r="J155" s="2"/>
     </row>
@@ -3455,7 +3292,6 @@
       <c r="E156" s="2">
         <v>96.0</v>
       </c>
-      <c r="G156" s="4"/>
       <c r="I156" s="2"/>
       <c r="J156" s="2"/>
     </row>
@@ -3475,7 +3311,6 @@
       <c r="E157" s="2">
         <v>159.0</v>
       </c>
-      <c r="G157" s="4"/>
       <c r="I157" s="2"/>
       <c r="J157" s="2"/>
     </row>
@@ -3495,7 +3330,6 @@
       <c r="E158" s="2">
         <v>185.0</v>
       </c>
-      <c r="G158" s="4"/>
       <c r="I158" s="2"/>
       <c r="J158" s="2"/>
     </row>
@@ -3515,7 +3349,6 @@
       <c r="E159" s="2">
         <v>259.0</v>
       </c>
-      <c r="G159" s="4"/>
       <c r="I159" s="2"/>
       <c r="J159" s="2"/>
     </row>
@@ -3535,7 +3368,6 @@
       <c r="E160" s="2">
         <v>265.0</v>
       </c>
-      <c r="G160" s="4"/>
       <c r="I160" s="2"/>
       <c r="J160" s="2"/>
     </row>
@@ -3555,7 +3387,6 @@
       <c r="E161" s="2">
         <v>66.0</v>
       </c>
-      <c r="G161" s="4"/>
       <c r="I161" s="2"/>
       <c r="J161" s="2"/>
     </row>
@@ -3575,7 +3406,6 @@
       <c r="E162" s="2">
         <v>77.0</v>
       </c>
-      <c r="G162" s="4"/>
       <c r="I162" s="2"/>
       <c r="J162" s="2"/>
     </row>
@@ -3595,7 +3425,6 @@
       <c r="E163" s="2">
         <v>99.0</v>
       </c>
-      <c r="G163" s="4"/>
       <c r="I163" s="2"/>
       <c r="J163" s="2"/>
     </row>
@@ -3615,7 +3444,6 @@
       <c r="E164" s="2">
         <v>164.0</v>
       </c>
-      <c r="G164" s="4"/>
       <c r="I164" s="2"/>
       <c r="J164" s="2"/>
     </row>
@@ -3635,7 +3463,6 @@
       <c r="E165" s="2">
         <v>196.0</v>
       </c>
-      <c r="G165" s="4"/>
       <c r="I165" s="2"/>
       <c r="J165" s="2"/>
     </row>
@@ -3655,7 +3482,6 @@
       <c r="E166" s="2">
         <v>275.0</v>
       </c>
-      <c r="G166" s="4"/>
       <c r="I166" s="2"/>
       <c r="J166" s="2"/>
     </row>
@@ -3675,7 +3501,6 @@
       <c r="E167" s="2">
         <v>279.0</v>
       </c>
-      <c r="G167" s="4"/>
       <c r="I167" s="2"/>
       <c r="J167" s="2"/>
     </row>
@@ -3695,7 +3520,6 @@
       <c r="E168" s="2">
         <v>67.0</v>
       </c>
-      <c r="G168" s="4"/>
       <c r="I168" s="2"/>
       <c r="J168" s="2"/>
     </row>
@@ -3715,7 +3539,6 @@
       <c r="E169" s="2">
         <v>79.0</v>
       </c>
-      <c r="G169" s="4"/>
       <c r="I169" s="2"/>
       <c r="J169" s="2"/>
     </row>
@@ -3735,7 +3558,6 @@
       <c r="E170" s="2">
         <v>100.0</v>
       </c>
-      <c r="G170" s="4"/>
       <c r="I170" s="2"/>
       <c r="J170" s="2"/>
     </row>
@@ -3755,7 +3577,6 @@
       <c r="E171" s="2">
         <v>166.0</v>
       </c>
-      <c r="G171" s="4"/>
       <c r="I171" s="2"/>
       <c r="J171" s="2"/>
     </row>
@@ -3775,7 +3596,6 @@
       <c r="E172" s="2">
         <v>205.0</v>
       </c>
-      <c r="G172" s="4"/>
       <c r="I172" s="2"/>
       <c r="J172" s="2"/>
     </row>
@@ -3795,7 +3615,6 @@
       <c r="E173" s="2">
         <v>289.0</v>
       </c>
-      <c r="G173" s="4"/>
       <c r="I173" s="2"/>
       <c r="J173" s="2"/>
     </row>
@@ -3815,7 +3634,6 @@
       <c r="E174" s="2">
         <v>295.0</v>
       </c>
-      <c r="G174" s="4"/>
       <c r="I174" s="2"/>
       <c r="J174" s="2"/>
     </row>
@@ -3835,7 +3653,6 @@
       <c r="E175" s="2">
         <v>69.0</v>
       </c>
-      <c r="G175" s="4"/>
       <c r="I175" s="2"/>
       <c r="J175" s="2"/>
     </row>
@@ -3855,7 +3672,6 @@
       <c r="E176" s="2">
         <v>79.0</v>
       </c>
-      <c r="G176" s="4"/>
       <c r="I176" s="2"/>
       <c r="J176" s="2"/>
     </row>
@@ -3875,7 +3691,6 @@
       <c r="E177" s="2">
         <v>105.0</v>
       </c>
-      <c r="G177" s="4"/>
       <c r="I177" s="2"/>
       <c r="J177" s="2"/>
     </row>
@@ -3895,7 +3710,6 @@
       <c r="E178" s="2">
         <v>167.0</v>
       </c>
-      <c r="G178" s="4"/>
       <c r="I178" s="2"/>
       <c r="J178" s="2"/>
     </row>
@@ -3915,7 +3729,6 @@
       <c r="E179" s="2">
         <v>207.0</v>
       </c>
-      <c r="G179" s="4"/>
       <c r="I179" s="2"/>
       <c r="J179" s="2"/>
     </row>
@@ -3935,7 +3748,6 @@
       <c r="E180" s="2">
         <v>291.0</v>
       </c>
-      <c r="G180" s="4"/>
       <c r="I180" s="2"/>
       <c r="J180" s="2"/>
     </row>
@@ -3955,7 +3767,6 @@
       <c r="E181" s="2">
         <v>297.0</v>
       </c>
-      <c r="G181" s="4"/>
       <c r="I181" s="2"/>
       <c r="J181" s="2"/>
     </row>
@@ -3975,7 +3786,6 @@
       <c r="E182" s="2">
         <v>83.0</v>
       </c>
-      <c r="G182" s="4"/>
       <c r="I182" s="2"/>
       <c r="J182" s="2"/>
     </row>
@@ -3995,7 +3805,6 @@
       <c r="E183" s="2">
         <v>99.0</v>
       </c>
-      <c r="G183" s="4"/>
       <c r="I183" s="2"/>
       <c r="J183" s="2"/>
     </row>
@@ -4015,7 +3824,6 @@
       <c r="E184" s="2">
         <v>121.0</v>
       </c>
-      <c r="G184" s="4"/>
       <c r="I184" s="2"/>
       <c r="J184" s="2"/>
     </row>
@@ -4035,7 +3843,6 @@
       <c r="E185" s="2">
         <v>169.0</v>
       </c>
-      <c r="G185" s="4"/>
       <c r="I185" s="2"/>
       <c r="J185" s="2"/>
     </row>
@@ -4055,7 +3862,6 @@
       <c r="E186" s="2">
         <v>207.0</v>
       </c>
-      <c r="G186" s="4"/>
       <c r="I186" s="2"/>
       <c r="J186" s="2"/>
     </row>
@@ -4075,7 +3881,6 @@
       <c r="E187" s="2">
         <v>273.0</v>
       </c>
-      <c r="G187" s="4"/>
       <c r="I187" s="2"/>
       <c r="J187" s="2"/>
     </row>
@@ -4092,10 +3897,9 @@
       <c r="D188" s="3">
         <v>2.0</v>
       </c>
-      <c r="E188" s="5">
-        <v>85.0</v>
-      </c>
-      <c r="G188" s="4"/>
+      <c r="E188" s="2">
+        <v>82.0</v>
+      </c>
       <c r="I188" s="2"/>
       <c r="J188" s="2"/>
     </row>
@@ -4115,7 +3919,6 @@
       <c r="E189" s="2">
         <v>103.0</v>
       </c>
-      <c r="G189" s="4"/>
       <c r="I189" s="2"/>
       <c r="J189" s="2"/>
     </row>
@@ -4135,7 +3938,6 @@
       <c r="E190" s="2">
         <v>124.0</v>
       </c>
-      <c r="G190" s="4"/>
       <c r="I190" s="2"/>
       <c r="J190" s="2"/>
     </row>
@@ -4155,7 +3957,6 @@
       <c r="E191" s="2">
         <v>176.0</v>
       </c>
-      <c r="G191" s="4"/>
       <c r="I191" s="2"/>
       <c r="J191" s="2"/>
     </row>
@@ -4175,7 +3976,6 @@
       <c r="E192" s="2">
         <v>217.0</v>
       </c>
-      <c r="G192" s="4"/>
       <c r="I192" s="2"/>
       <c r="J192" s="2"/>
     </row>
@@ -4195,7 +3995,6 @@
       <c r="E193" s="2">
         <v>284.0</v>
       </c>
-      <c r="G193" s="4"/>
       <c r="I193" s="2"/>
       <c r="J193" s="2"/>
     </row>
@@ -4215,7 +4014,6 @@
       <c r="E194" s="2">
         <v>86.0</v>
       </c>
-      <c r="G194" s="4"/>
       <c r="I194" s="2"/>
       <c r="J194" s="2"/>
     </row>
@@ -4235,7 +4033,6 @@
       <c r="E195" s="2">
         <v>104.0</v>
       </c>
-      <c r="G195" s="4"/>
       <c r="I195" s="2"/>
       <c r="J195" s="2"/>
     </row>
@@ -4255,7 +4052,6 @@
       <c r="E196" s="2">
         <v>126.5</v>
       </c>
-      <c r="G196" s="4"/>
       <c r="I196" s="2"/>
       <c r="J196" s="2"/>
     </row>
@@ -4275,7 +4071,6 @@
       <c r="E197" s="2">
         <v>179.0</v>
       </c>
-      <c r="G197" s="4"/>
       <c r="I197" s="2"/>
       <c r="J197" s="2"/>
     </row>
@@ -4295,7 +4090,6 @@
       <c r="E198" s="2">
         <v>223.0</v>
       </c>
-      <c r="G198" s="4"/>
       <c r="I198" s="2"/>
       <c r="J198" s="2"/>
     </row>
@@ -4315,7 +4109,6 @@
       <c r="E199" s="2">
         <v>288.0</v>
       </c>
-      <c r="G199" s="4"/>
       <c r="I199" s="2"/>
       <c r="J199" s="2"/>
     </row>
@@ -4335,7 +4128,6 @@
       <c r="E200" s="2">
         <v>87.0</v>
       </c>
-      <c r="G200" s="4"/>
       <c r="I200" s="2"/>
       <c r="J200" s="2"/>
     </row>
@@ -4355,7 +4147,6 @@
       <c r="E201" s="2">
         <v>105.5</v>
       </c>
-      <c r="G201" s="4"/>
       <c r="I201" s="2"/>
       <c r="J201" s="2"/>
     </row>
@@ -4375,7 +4166,6 @@
       <c r="E202" s="2">
         <v>131.0</v>
       </c>
-      <c r="G202" s="4"/>
       <c r="I202" s="2"/>
       <c r="J202" s="2"/>
     </row>
@@ -4395,7 +4185,6 @@
       <c r="E203" s="2">
         <v>181.0</v>
       </c>
-      <c r="G203" s="4"/>
       <c r="I203" s="2"/>
       <c r="J203" s="2"/>
     </row>
@@ -4415,7 +4204,6 @@
       <c r="E204" s="2">
         <v>227.0</v>
       </c>
-      <c r="G204" s="4"/>
       <c r="I204" s="2"/>
       <c r="J204" s="2"/>
     </row>
@@ -4435,7 +4223,6 @@
       <c r="E205" s="2">
         <v>294.0</v>
       </c>
-      <c r="G205" s="4"/>
       <c r="I205" s="2"/>
       <c r="J205" s="2"/>
     </row>
@@ -4455,7 +4242,6 @@
       <c r="E206" s="2">
         <v>88.5</v>
       </c>
-      <c r="G206" s="4"/>
       <c r="I206" s="2"/>
       <c r="J206" s="2"/>
     </row>
@@ -4475,7 +4261,6 @@
       <c r="E207" s="2">
         <v>108.5</v>
       </c>
-      <c r="G207" s="4"/>
       <c r="I207" s="2"/>
       <c r="J207" s="2"/>
     </row>
@@ -4495,7 +4280,6 @@
       <c r="E208" s="2">
         <v>135.5</v>
       </c>
-      <c r="G208" s="4"/>
       <c r="I208" s="2"/>
       <c r="J208" s="2"/>
     </row>
@@ -4515,7 +4299,6 @@
       <c r="E209" s="2">
         <v>189.0</v>
       </c>
-      <c r="G209" s="4"/>
       <c r="I209" s="2"/>
       <c r="J209" s="2"/>
     </row>
@@ -4535,7 +4318,6 @@
       <c r="E210" s="2">
         <v>243.0</v>
       </c>
-      <c r="G210" s="4"/>
       <c r="I210" s="2"/>
       <c r="J210" s="2"/>
     </row>
@@ -4555,7 +4337,6 @@
       <c r="E211" s="2">
         <v>315.0</v>
       </c>
-      <c r="G211" s="4"/>
       <c r="I211" s="2"/>
       <c r="J211" s="2"/>
     </row>
@@ -4575,7 +4356,6 @@
       <c r="E212" s="2">
         <v>89.5</v>
       </c>
-      <c r="G212" s="4"/>
       <c r="I212" s="2"/>
       <c r="J212" s="2"/>
     </row>
@@ -4595,7 +4375,6 @@
       <c r="E213" s="2">
         <v>111.0</v>
       </c>
-      <c r="G213" s="4"/>
       <c r="I213" s="2"/>
       <c r="J213" s="2"/>
     </row>
@@ -4615,7 +4394,6 @@
       <c r="E214" s="2">
         <v>137.0</v>
       </c>
-      <c r="G214" s="4"/>
       <c r="I214" s="2"/>
       <c r="J214" s="2"/>
     </row>
@@ -4635,7 +4413,6 @@
       <c r="E215" s="2">
         <v>192.0</v>
       </c>
-      <c r="G215" s="4"/>
       <c r="I215" s="2"/>
       <c r="J215" s="2"/>
     </row>
@@ -4655,7 +4432,6 @@
       <c r="E216" s="2">
         <v>247.0</v>
       </c>
-      <c r="G216" s="4"/>
       <c r="I216" s="2"/>
       <c r="J216" s="2"/>
     </row>
@@ -4675,7 +4451,6 @@
       <c r="E217" s="2">
         <v>318.0</v>
       </c>
-      <c r="G217" s="4"/>
       <c r="I217" s="2"/>
       <c r="J217" s="2"/>
     </row>
@@ -4695,7 +4470,6 @@
       <c r="E218" s="2">
         <v>90.0</v>
       </c>
-      <c r="G218" s="4"/>
       <c r="I218" s="2"/>
       <c r="J218" s="2"/>
     </row>
@@ -4715,7 +4489,6 @@
       <c r="E219" s="2">
         <v>106.0</v>
       </c>
-      <c r="G219" s="4"/>
       <c r="I219" s="2"/>
       <c r="J219" s="2"/>
     </row>
@@ -4735,7 +4508,6 @@
       <c r="E220" s="2">
         <v>112.0</v>
       </c>
-      <c r="G220" s="4"/>
       <c r="I220" s="2"/>
       <c r="J220" s="2"/>
     </row>
@@ -4755,7 +4527,6 @@
       <c r="E221" s="2">
         <v>174.0</v>
       </c>
-      <c r="G221" s="4"/>
       <c r="I221" s="2"/>
       <c r="J221" s="2"/>
     </row>
@@ -4775,7 +4546,6 @@
       <c r="E222" s="2">
         <v>206.0</v>
       </c>
-      <c r="G222" s="4"/>
       <c r="I222" s="2"/>
       <c r="J222" s="2"/>
     </row>
@@ -4795,7 +4565,6 @@
       <c r="E223" s="2">
         <v>293.0</v>
       </c>
-      <c r="G223" s="4"/>
       <c r="I223" s="2"/>
       <c r="J223" s="2"/>
     </row>
@@ -4815,7 +4584,6 @@
       <c r="E224" s="2">
         <v>304.0</v>
       </c>
-      <c r="G224" s="4"/>
       <c r="I224" s="2"/>
       <c r="J224" s="2"/>
     </row>
@@ -4835,7 +4603,6 @@
       <c r="E225" s="2">
         <v>93.0</v>
       </c>
-      <c r="G225" s="4"/>
       <c r="I225" s="2"/>
       <c r="J225" s="2"/>
     </row>
@@ -4855,7 +4622,6 @@
       <c r="E226" s="2">
         <v>110.0</v>
       </c>
-      <c r="G226" s="4"/>
       <c r="I226" s="2"/>
       <c r="J226" s="2"/>
     </row>
@@ -4875,7 +4641,6 @@
       <c r="E227" s="2">
         <v>118.0</v>
       </c>
-      <c r="G227" s="4"/>
       <c r="I227" s="2"/>
       <c r="J227" s="2"/>
     </row>
@@ -4895,7 +4660,6 @@
       <c r="E228" s="2">
         <v>180.0</v>
       </c>
-      <c r="G228" s="4"/>
       <c r="I228" s="2"/>
       <c r="J228" s="2"/>
     </row>
@@ -4915,7 +4679,6 @@
       <c r="E229" s="2">
         <v>210.0</v>
       </c>
-      <c r="G229" s="4"/>
       <c r="I229" s="2"/>
       <c r="J229" s="2"/>
     </row>
@@ -4935,7 +4698,6 @@
       <c r="E230" s="2">
         <v>301.0</v>
       </c>
-      <c r="G230" s="4"/>
       <c r="I230" s="2"/>
       <c r="J230" s="2"/>
     </row>
@@ -4955,7 +4717,6 @@
       <c r="E231" s="2">
         <v>309.0</v>
       </c>
-      <c r="G231" s="4"/>
       <c r="I231" s="2"/>
       <c r="J231" s="2"/>
     </row>
@@ -4975,7 +4736,6 @@
       <c r="E232" s="2">
         <v>94.0</v>
       </c>
-      <c r="G232" s="4"/>
       <c r="I232" s="2"/>
       <c r="J232" s="2"/>
     </row>
@@ -4995,7 +4755,6 @@
       <c r="E233" s="2">
         <v>111.0</v>
       </c>
-      <c r="G233" s="4"/>
       <c r="I233" s="2"/>
       <c r="J233" s="2"/>
     </row>
@@ -5015,7 +4774,6 @@
       <c r="E234" s="2">
         <v>119.0</v>
       </c>
-      <c r="G234" s="4"/>
       <c r="I234" s="2"/>
       <c r="J234" s="2"/>
     </row>
@@ -5035,7 +4793,6 @@
       <c r="E235" s="2">
         <v>185.0</v>
       </c>
-      <c r="G235" s="4"/>
       <c r="I235" s="2"/>
       <c r="J235" s="2"/>
     </row>
@@ -5055,7 +4812,6 @@
       <c r="E236" s="2">
         <v>215.0</v>
       </c>
-      <c r="G236" s="4"/>
       <c r="I236" s="2"/>
       <c r="J236" s="2"/>
     </row>
@@ -5075,7 +4831,6 @@
       <c r="E237" s="2">
         <v>308.0</v>
       </c>
-      <c r="G237" s="4"/>
       <c r="I237" s="2"/>
       <c r="J237" s="2"/>
     </row>
@@ -5095,7 +4850,6 @@
       <c r="E238" s="2">
         <v>319.0</v>
       </c>
-      <c r="G238" s="4"/>
       <c r="I238" s="2"/>
       <c r="J238" s="2"/>
     </row>
@@ -5115,7 +4869,6 @@
       <c r="E239" s="2">
         <v>102.0</v>
       </c>
-      <c r="G239" s="4"/>
       <c r="I239" s="2"/>
       <c r="J239" s="2"/>
     </row>
@@ -5135,7 +4888,6 @@
       <c r="E240" s="2">
         <v>120.0</v>
       </c>
-      <c r="G240" s="4"/>
       <c r="I240" s="2"/>
       <c r="J240" s="2"/>
     </row>
@@ -5155,7 +4907,6 @@
       <c r="E241" s="2">
         <v>129.0</v>
       </c>
-      <c r="G241" s="4"/>
       <c r="I241" s="2"/>
       <c r="J241" s="2"/>
     </row>
@@ -5175,7 +4926,6 @@
       <c r="E242" s="2">
         <v>198.0</v>
       </c>
-      <c r="G242" s="4"/>
       <c r="I242" s="2"/>
       <c r="J242" s="2"/>
     </row>
@@ -5195,7 +4945,6 @@
       <c r="E243" s="2">
         <v>228.0</v>
       </c>
-      <c r="G243" s="4"/>
       <c r="I243" s="2"/>
       <c r="J243" s="2"/>
     </row>
@@ -5215,7 +4964,6 @@
       <c r="E244" s="2">
         <v>320.0</v>
       </c>
-      <c r="G244" s="4"/>
       <c r="I244" s="2"/>
       <c r="J244" s="2"/>
     </row>
@@ -5235,7 +4983,6 @@
       <c r="E245" s="2">
         <v>329.0</v>
       </c>
-      <c r="G245" s="4"/>
       <c r="I245" s="2"/>
       <c r="J245" s="2"/>
     </row>
@@ -5255,7 +5002,6 @@
       <c r="E246" s="2">
         <v>102.5</v>
       </c>
-      <c r="G246" s="4"/>
       <c r="I246" s="2"/>
       <c r="J246" s="2"/>
     </row>
@@ -5275,7 +5021,6 @@
       <c r="E247" s="2">
         <v>120.5</v>
       </c>
-      <c r="G247" s="4"/>
       <c r="I247" s="2"/>
       <c r="J247" s="2"/>
     </row>
@@ -5295,7 +5040,6 @@
       <c r="E248" s="2">
         <v>130.0</v>
       </c>
-      <c r="G248" s="4"/>
       <c r="I248" s="2"/>
       <c r="J248" s="2"/>
     </row>
@@ -5315,7 +5059,6 @@
       <c r="E249" s="2">
         <v>198.5</v>
       </c>
-      <c r="G249" s="4"/>
       <c r="I249" s="2"/>
       <c r="J249" s="2"/>
     </row>
@@ -5335,7 +5078,6 @@
       <c r="E250" s="2">
         <v>228.5</v>
       </c>
-      <c r="G250" s="4"/>
       <c r="I250" s="2"/>
       <c r="J250" s="2"/>
     </row>
@@ -5355,7 +5097,6 @@
       <c r="E251" s="2">
         <v>321.0</v>
       </c>
-      <c r="G251" s="4"/>
       <c r="I251" s="2"/>
       <c r="J251" s="2"/>
     </row>
@@ -5375,7 +5116,6 @@
       <c r="E252" s="2">
         <v>330.0</v>
       </c>
-      <c r="G252" s="4"/>
       <c r="I252" s="2"/>
       <c r="J252" s="2"/>
     </row>
@@ -5395,7 +5135,6 @@
       <c r="E253" s="2">
         <v>104.0</v>
       </c>
-      <c r="G253" s="4"/>
       <c r="I253" s="2"/>
       <c r="J253" s="2"/>
     </row>
@@ -5415,7 +5154,6 @@
       <c r="E254" s="2">
         <v>122.0</v>
       </c>
-      <c r="G254" s="4"/>
       <c r="I254" s="2"/>
       <c r="J254" s="2"/>
     </row>
@@ -5435,7 +5173,6 @@
       <c r="E255" s="2">
         <v>132.0</v>
       </c>
-      <c r="G255" s="4"/>
       <c r="I255" s="2"/>
       <c r="J255" s="2"/>
     </row>
@@ -5455,7 +5192,6 @@
       <c r="E256" s="2">
         <v>203.0</v>
       </c>
-      <c r="G256" s="4"/>
       <c r="I256" s="2"/>
       <c r="J256" s="2"/>
     </row>
@@ -5475,7 +5211,6 @@
       <c r="E257" s="2">
         <v>233.0</v>
       </c>
-      <c r="G257" s="4"/>
       <c r="I257" s="2"/>
       <c r="J257" s="2"/>
     </row>
@@ -5495,7 +5230,6 @@
       <c r="E258" s="2">
         <v>330.0</v>
       </c>
-      <c r="G258" s="4"/>
       <c r="I258" s="2"/>
       <c r="J258" s="2"/>
     </row>
@@ -5515,7 +5249,6 @@
       <c r="E259" s="2">
         <v>340.0</v>
       </c>
-      <c r="G259" s="4"/>
       <c r="I259" s="2"/>
       <c r="J259" s="2"/>
     </row>
@@ -5535,7 +5268,6 @@
       <c r="E260" s="2">
         <v>0.0</v>
       </c>
-      <c r="G260" s="6"/>
       <c r="I260" s="2"/>
       <c r="J260" s="2"/>
     </row>
@@ -5555,7 +5287,6 @@
       <c r="E261" s="2">
         <v>67.5</v>
       </c>
-      <c r="G261" s="4"/>
       <c r="I261" s="2"/>
       <c r="J261" s="2"/>
     </row>
@@ -5575,7 +5306,6 @@
       <c r="E262" s="2">
         <v>67.5</v>
       </c>
-      <c r="G262" s="4"/>
       <c r="I262" s="2"/>
       <c r="J262" s="2"/>
     </row>
@@ -5595,7 +5325,6 @@
       <c r="E263" s="2">
         <v>86.0</v>
       </c>
-      <c r="G263" s="4"/>
       <c r="I263" s="2"/>
       <c r="J263" s="2"/>
     </row>
@@ -5615,7 +5344,6 @@
       <c r="E264" s="2">
         <v>103.0</v>
       </c>
-      <c r="G264" s="4"/>
       <c r="I264" s="2"/>
       <c r="J264" s="2"/>
     </row>
@@ -5635,7 +5363,6 @@
       <c r="E265" s="2">
         <v>133.0</v>
       </c>
-      <c r="G265" s="4"/>
       <c r="I265" s="2"/>
       <c r="J265" s="2"/>
     </row>
@@ -5655,7 +5382,6 @@
       <c r="E266" s="2">
         <v>162.0</v>
       </c>
-      <c r="G266" s="4"/>
       <c r="I266" s="2"/>
       <c r="J266" s="2"/>
     </row>
@@ -5675,7 +5401,6 @@
       <c r="E267" s="2">
         <v>170.0</v>
       </c>
-      <c r="G267" s="4"/>
       <c r="I267" s="2"/>
       <c r="J267" s="2"/>
     </row>
@@ -5695,7 +5420,6 @@
       <c r="E268" s="2">
         <v>0.0</v>
       </c>
-      <c r="G268" s="6"/>
       <c r="I268" s="2"/>
       <c r="J268" s="2"/>
     </row>
@@ -5715,7 +5439,6 @@
       <c r="E269" s="2">
         <v>70.0</v>
       </c>
-      <c r="G269" s="4"/>
       <c r="I269" s="2"/>
       <c r="J269" s="2"/>
     </row>
@@ -5735,7 +5458,6 @@
       <c r="E270" s="2">
         <v>70.0</v>
       </c>
-      <c r="G270" s="4"/>
       <c r="I270" s="2"/>
       <c r="J270" s="2"/>
     </row>
@@ -5755,7 +5477,6 @@
       <c r="E271" s="2">
         <v>88.0</v>
       </c>
-      <c r="G271" s="4"/>
       <c r="I271" s="2"/>
       <c r="J271" s="2"/>
     </row>
@@ -5775,7 +5496,6 @@
       <c r="E272" s="2">
         <v>105.0</v>
       </c>
-      <c r="G272" s="4"/>
       <c r="I272" s="2"/>
       <c r="J272" s="2"/>
     </row>
@@ -5795,7 +5515,6 @@
       <c r="E273" s="2">
         <v>138.0</v>
       </c>
-      <c r="G273" s="4"/>
       <c r="I273" s="2"/>
       <c r="J273" s="2"/>
     </row>
@@ -5815,7 +5534,6 @@
       <c r="E274" s="2">
         <v>167.0</v>
       </c>
-      <c r="G274" s="4"/>
       <c r="I274" s="2"/>
       <c r="J274" s="2"/>
     </row>
@@ -5835,7 +5553,6 @@
       <c r="E275" s="2">
         <v>175.0</v>
       </c>
-      <c r="G275" s="4"/>
       <c r="I275" s="2"/>
       <c r="J275" s="2"/>
     </row>
@@ -5855,7 +5572,6 @@
       <c r="E276" s="2">
         <v>0.0</v>
       </c>
-      <c r="G276" s="6"/>
       <c r="I276" s="2"/>
       <c r="J276" s="2"/>
     </row>
@@ -5875,7 +5591,6 @@
       <c r="E277" s="2">
         <v>71.0</v>
       </c>
-      <c r="G277" s="4"/>
       <c r="I277" s="2"/>
       <c r="J277" s="2"/>
     </row>
@@ -5895,7 +5610,6 @@
       <c r="E278" s="2">
         <v>71.0</v>
       </c>
-      <c r="G278" s="4"/>
       <c r="I278" s="2"/>
       <c r="J278" s="2"/>
     </row>
@@ -5915,7 +5629,6 @@
       <c r="E279" s="2">
         <v>89.5</v>
       </c>
-      <c r="G279" s="4"/>
       <c r="I279" s="2"/>
       <c r="J279" s="2"/>
     </row>
@@ -5935,7 +5648,6 @@
       <c r="E280" s="2">
         <v>106.0</v>
       </c>
-      <c r="G280" s="4"/>
       <c r="I280" s="2"/>
       <c r="J280" s="2"/>
     </row>
@@ -5955,7 +5667,6 @@
       <c r="E281" s="2">
         <v>140.0</v>
       </c>
-      <c r="G281" s="4"/>
       <c r="I281" s="2"/>
       <c r="J281" s="2"/>
     </row>
@@ -5975,7 +5686,6 @@
       <c r="E282" s="2">
         <v>170.0</v>
       </c>
-      <c r="G282" s="4"/>
       <c r="I282" s="2"/>
       <c r="J282" s="2"/>
     </row>
@@ -5995,7 +5705,6 @@
       <c r="E283" s="2">
         <v>177.0</v>
       </c>
-      <c r="G283" s="4"/>
       <c r="I283" s="2"/>
       <c r="J283" s="2"/>
     </row>
@@ -6015,7 +5724,6 @@
       <c r="E284" s="2">
         <v>0.0</v>
       </c>
-      <c r="G284" s="6"/>
       <c r="I284" s="2"/>
       <c r="J284" s="2"/>
     </row>
@@ -6035,7 +5743,6 @@
       <c r="E285" s="2">
         <v>72.0</v>
       </c>
-      <c r="G285" s="4"/>
       <c r="I285" s="2"/>
       <c r="J285" s="2"/>
     </row>
@@ -6055,7 +5762,6 @@
       <c r="E286" s="2">
         <v>72.0</v>
       </c>
-      <c r="G286" s="4"/>
       <c r="I286" s="2"/>
       <c r="J286" s="2"/>
     </row>
@@ -6075,7 +5781,6 @@
       <c r="E287" s="2">
         <v>92.0</v>
       </c>
-      <c r="G287" s="4"/>
       <c r="I287" s="2"/>
       <c r="J287" s="2"/>
     </row>
@@ -6095,7 +5800,6 @@
       <c r="E288" s="2">
         <v>111.0</v>
       </c>
-      <c r="G288" s="4"/>
       <c r="I288" s="2"/>
       <c r="J288" s="2"/>
     </row>
@@ -6115,7 +5819,6 @@
       <c r="E289" s="2">
         <v>145.0</v>
       </c>
-      <c r="G289" s="4"/>
       <c r="I289" s="2"/>
       <c r="J289" s="2"/>
     </row>
@@ -6135,7 +5838,6 @@
       <c r="E290" s="2">
         <v>175.0</v>
       </c>
-      <c r="G290" s="4"/>
       <c r="I290" s="2"/>
       <c r="J290" s="2"/>
     </row>
@@ -6155,7 +5857,6 @@
       <c r="E291" s="2">
         <v>182.0</v>
       </c>
-      <c r="G291" s="4"/>
       <c r="I291" s="2"/>
       <c r="J291" s="2"/>
     </row>
@@ -6175,7 +5876,6 @@
       <c r="E292" s="2">
         <v>0.0</v>
       </c>
-      <c r="G292" s="6"/>
       <c r="I292" s="2"/>
       <c r="J292" s="2"/>
     </row>
@@ -6195,7 +5895,6 @@
       <c r="E293" s="2">
         <v>73.0</v>
       </c>
-      <c r="G293" s="4"/>
       <c r="I293" s="2"/>
       <c r="J293" s="2"/>
     </row>
@@ -6215,7 +5914,6 @@
       <c r="E294" s="2">
         <v>73.0</v>
       </c>
-      <c r="G294" s="4"/>
       <c r="I294" s="2"/>
       <c r="J294" s="2"/>
     </row>
@@ -6235,7 +5933,6 @@
       <c r="E295" s="2">
         <v>93.0</v>
       </c>
-      <c r="G295" s="4"/>
       <c r="I295" s="2"/>
       <c r="J295" s="2"/>
     </row>
@@ -6255,7 +5952,6 @@
       <c r="E296" s="2">
         <v>113.0</v>
       </c>
-      <c r="G296" s="4"/>
       <c r="I296" s="2"/>
       <c r="J296" s="2"/>
     </row>
@@ -6275,7 +5971,6 @@
       <c r="E297" s="2">
         <v>149.0</v>
       </c>
-      <c r="G297" s="4"/>
       <c r="I297" s="2"/>
       <c r="J297" s="2"/>
     </row>
@@ -6295,7 +5990,6 @@
       <c r="E298" s="2">
         <v>179.0</v>
       </c>
-      <c r="G298" s="4"/>
       <c r="I298" s="2"/>
       <c r="J298" s="2"/>
     </row>
@@ -6315,7 +6009,6 @@
       <c r="E299" s="2">
         <v>188.0</v>
       </c>
-      <c r="G299" s="4"/>
       <c r="I299" s="2"/>
       <c r="J299" s="2"/>
     </row>
@@ -6335,7 +6028,6 @@
       <c r="E300" s="2">
         <v>0.0</v>
       </c>
-      <c r="G300" s="6"/>
       <c r="I300" s="2"/>
       <c r="J300" s="2"/>
     </row>
@@ -6355,7 +6047,6 @@
       <c r="E301" s="2">
         <v>74.0</v>
       </c>
-      <c r="G301" s="4"/>
       <c r="I301" s="2"/>
       <c r="J301" s="2"/>
     </row>
@@ -6375,7 +6066,6 @@
       <c r="E302" s="2">
         <v>74.0</v>
       </c>
-      <c r="G302" s="4"/>
       <c r="I302" s="2"/>
       <c r="J302" s="2"/>
     </row>
@@ -6395,7 +6085,6 @@
       <c r="E303" s="2">
         <v>94.0</v>
       </c>
-      <c r="G303" s="4"/>
       <c r="I303" s="2"/>
       <c r="J303" s="2"/>
     </row>
@@ -6415,7 +6104,6 @@
       <c r="E304" s="2">
         <v>115.0</v>
       </c>
-      <c r="G304" s="4"/>
       <c r="I304" s="2"/>
       <c r="J304" s="2"/>
     </row>
@@ -6435,7 +6123,6 @@
       <c r="E305" s="2">
         <v>150.0</v>
       </c>
-      <c r="G305" s="4"/>
       <c r="I305" s="2"/>
       <c r="J305" s="2"/>
     </row>
@@ -6455,7 +6142,6 @@
       <c r="E306" s="2">
         <v>183.0</v>
       </c>
-      <c r="G306" s="4"/>
       <c r="I306" s="2"/>
       <c r="J306" s="2"/>
     </row>
@@ -6475,7 +6161,6 @@
       <c r="E307" s="2">
         <v>190.0</v>
       </c>
-      <c r="G307" s="4"/>
       <c r="I307" s="2"/>
       <c r="J307" s="2"/>
     </row>
@@ -6495,7 +6180,6 @@
       <c r="E308" s="2">
         <v>0.0</v>
       </c>
-      <c r="G308" s="6"/>
       <c r="I308" s="2"/>
       <c r="J308" s="2"/>
     </row>
@@ -6515,7 +6199,6 @@
       <c r="E309" s="2">
         <v>101.0</v>
       </c>
-      <c r="G309" s="4"/>
       <c r="I309" s="2"/>
       <c r="J309" s="2"/>
     </row>
@@ -6535,7 +6218,6 @@
       <c r="E310" s="2">
         <v>101.0</v>
       </c>
-      <c r="G310" s="4"/>
       <c r="I310" s="2"/>
       <c r="J310" s="2"/>
     </row>
@@ -6555,7 +6237,6 @@
       <c r="E311" s="2">
         <v>138.0</v>
       </c>
-      <c r="G311" s="4"/>
       <c r="I311" s="2"/>
       <c r="J311" s="2"/>
     </row>
@@ -6575,7 +6256,6 @@
       <c r="E312" s="2">
         <v>172.0</v>
       </c>
-      <c r="G312" s="4"/>
       <c r="I312" s="2"/>
       <c r="J312" s="2"/>
     </row>
@@ -6595,7 +6275,6 @@
       <c r="E313" s="2">
         <v>231.0</v>
       </c>
-      <c r="G313" s="4"/>
       <c r="I313" s="2"/>
       <c r="J313" s="2"/>
     </row>
@@ -6615,7 +6294,6 @@
       <c r="E314" s="2">
         <v>0.0</v>
       </c>
-      <c r="G314" s="6"/>
       <c r="I314" s="2"/>
       <c r="J314" s="2"/>
     </row>
@@ -6635,7 +6313,6 @@
       <c r="E315" s="2">
         <v>104.0</v>
       </c>
-      <c r="G315" s="4"/>
       <c r="I315" s="2"/>
       <c r="J315" s="2"/>
     </row>
@@ -6655,7 +6332,6 @@
       <c r="E316" s="2">
         <v>104.0</v>
       </c>
-      <c r="G316" s="4"/>
       <c r="I316" s="2"/>
       <c r="J316" s="2"/>
     </row>
@@ -6675,7 +6351,6 @@
       <c r="E317" s="2">
         <v>142.0</v>
       </c>
-      <c r="G317" s="4"/>
       <c r="I317" s="2"/>
       <c r="J317" s="2"/>
     </row>
@@ -6695,7 +6370,6 @@
       <c r="E318" s="2">
         <v>176.0</v>
       </c>
-      <c r="G318" s="4"/>
       <c r="I318" s="2"/>
       <c r="J318" s="2"/>
     </row>
@@ -6715,7 +6389,6 @@
       <c r="E319" s="2">
         <v>239.0</v>
       </c>
-      <c r="G319" s="4"/>
       <c r="I319" s="2"/>
       <c r="J319" s="2"/>
     </row>
@@ -6735,7 +6408,6 @@
       <c r="E320" s="2">
         <v>0.0</v>
       </c>
-      <c r="G320" s="6"/>
       <c r="I320" s="2"/>
       <c r="J320" s="2"/>
     </row>
@@ -6755,7 +6427,6 @@
       <c r="E321" s="2">
         <v>105.0</v>
       </c>
-      <c r="G321" s="4"/>
       <c r="I321" s="2"/>
       <c r="J321" s="2"/>
     </row>
@@ -6775,7 +6446,6 @@
       <c r="E322" s="2">
         <v>105.0</v>
       </c>
-      <c r="G322" s="4"/>
       <c r="I322" s="2"/>
       <c r="J322" s="2"/>
     </row>
@@ -6795,7 +6465,6 @@
       <c r="E323" s="2">
         <v>144.0</v>
       </c>
-      <c r="G323" s="4"/>
       <c r="I323" s="2"/>
       <c r="J323" s="2"/>
     </row>
@@ -6815,7 +6484,6 @@
       <c r="E324" s="2">
         <v>180.0</v>
       </c>
-      <c r="G324" s="4"/>
       <c r="I324" s="2"/>
       <c r="J324" s="2"/>
     </row>
@@ -6835,7 +6503,6 @@
       <c r="E325" s="2">
         <v>245.0</v>
       </c>
-      <c r="G325" s="4"/>
       <c r="I325" s="2"/>
       <c r="J325" s="2"/>
     </row>
@@ -6855,7 +6522,6 @@
       <c r="E326" s="2">
         <v>0.0</v>
       </c>
-      <c r="G326" s="6"/>
       <c r="I326" s="2"/>
       <c r="J326" s="2"/>
     </row>
@@ -6875,7 +6541,6 @@
       <c r="E327" s="2">
         <v>110.0</v>
       </c>
-      <c r="G327" s="4"/>
       <c r="I327" s="2"/>
       <c r="J327" s="2"/>
     </row>
@@ -6895,7 +6560,6 @@
       <c r="E328" s="2">
         <v>110.0</v>
       </c>
-      <c r="G328" s="4"/>
       <c r="I328" s="2"/>
       <c r="J328" s="2"/>
     </row>
@@ -6915,7 +6579,6 @@
       <c r="E329" s="2">
         <v>145.0</v>
       </c>
-      <c r="G329" s="4"/>
       <c r="I329" s="2"/>
       <c r="J329" s="2"/>
     </row>
@@ -6935,7 +6598,6 @@
       <c r="E330" s="2">
         <v>184.0</v>
       </c>
-      <c r="G330" s="4"/>
       <c r="I330" s="2"/>
       <c r="J330" s="2"/>
     </row>
@@ -6955,7 +6617,6 @@
       <c r="E331" s="2">
         <v>252.0</v>
       </c>
-      <c r="G331" s="4"/>
       <c r="I331" s="2"/>
       <c r="J331" s="2"/>
     </row>
@@ -6975,7 +6636,6 @@
       <c r="E332" s="2">
         <v>0.0</v>
       </c>
-      <c r="G332" s="6"/>
       <c r="I332" s="2"/>
       <c r="J332" s="2"/>
     </row>
@@ -6995,7 +6655,6 @@
       <c r="E333" s="2">
         <v>113.0</v>
       </c>
-      <c r="G333" s="4"/>
       <c r="I333" s="2"/>
       <c r="J333" s="2"/>
     </row>
@@ -7015,7 +6674,6 @@
       <c r="E334" s="2">
         <v>113.0</v>
       </c>
-      <c r="G334" s="4"/>
       <c r="I334" s="2"/>
       <c r="J334" s="2"/>
     </row>
@@ -7035,7 +6693,6 @@
       <c r="E335" s="2">
         <v>151.5</v>
       </c>
-      <c r="G335" s="4"/>
       <c r="I335" s="2"/>
       <c r="J335" s="2"/>
     </row>
@@ -7055,7 +6712,6 @@
       <c r="E336" s="2">
         <v>190.0</v>
       </c>
-      <c r="G336" s="4"/>
       <c r="I336" s="2"/>
       <c r="J336" s="2"/>
     </row>
@@ -7075,7 +6731,6 @@
       <c r="E337" s="2">
         <v>254.0</v>
       </c>
-      <c r="G337" s="4"/>
       <c r="I337" s="2"/>
       <c r="J337" s="2"/>
     </row>
@@ -7095,7 +6750,6 @@
       <c r="E338" s="2">
         <v>0.0</v>
       </c>
-      <c r="G338" s="6"/>
       <c r="I338" s="2"/>
       <c r="J338" s="2"/>
     </row>
@@ -7115,7 +6769,6 @@
       <c r="E339" s="2">
         <v>116.0</v>
       </c>
-      <c r="G339" s="4"/>
       <c r="I339" s="2"/>
       <c r="J339" s="2"/>
     </row>
@@ -7135,7 +6788,6 @@
       <c r="E340" s="2">
         <v>116.0</v>
       </c>
-      <c r="G340" s="4"/>
       <c r="I340" s="2"/>
       <c r="J340" s="2"/>
     </row>
@@ -7155,7 +6807,6 @@
       <c r="E341" s="2">
         <v>155.0</v>
       </c>
-      <c r="G341" s="4"/>
       <c r="I341" s="2"/>
       <c r="J341" s="2"/>
     </row>
@@ -7175,7 +6826,6 @@
       <c r="E342" s="2">
         <v>195.0</v>
       </c>
-      <c r="G342" s="4"/>
       <c r="I342" s="2"/>
       <c r="J342" s="2"/>
     </row>
@@ -7195,7 +6845,6 @@
       <c r="E343" s="2">
         <v>259.0</v>
       </c>
-      <c r="G343" s="4"/>
       <c r="I343" s="2"/>
       <c r="J343" s="2"/>
     </row>
@@ -7215,7 +6864,6 @@
       <c r="E344" s="2">
         <v>55.5</v>
       </c>
-      <c r="G344" s="4"/>
       <c r="I344" s="2"/>
       <c r="J344" s="2"/>
     </row>
@@ -7235,7 +6883,6 @@
       <c r="E345" s="2">
         <v>61.0</v>
       </c>
-      <c r="G345" s="4"/>
       <c r="I345" s="2"/>
       <c r="J345" s="2"/>
     </row>
@@ -7255,7 +6902,6 @@
       <c r="E346" s="2">
         <v>79.0</v>
       </c>
-      <c r="G346" s="4"/>
       <c r="I346" s="2"/>
       <c r="J346" s="2"/>
     </row>
@@ -7275,7 +6921,6 @@
       <c r="E347" s="2">
         <v>123.0</v>
       </c>
-      <c r="G347" s="4"/>
       <c r="I347" s="2"/>
       <c r="J347" s="2"/>
     </row>
@@ -7295,7 +6940,6 @@
       <c r="E348" s="2">
         <v>153.0</v>
       </c>
-      <c r="G348" s="4"/>
       <c r="I348" s="2"/>
       <c r="J348" s="2"/>
     </row>
@@ -7315,7 +6959,6 @@
       <c r="E349" s="2">
         <v>235.0</v>
       </c>
-      <c r="G349" s="4"/>
       <c r="I349" s="2"/>
       <c r="J349" s="2"/>
     </row>
@@ -7335,7 +6978,6 @@
       <c r="E350" s="2">
         <v>239.0</v>
       </c>
-      <c r="G350" s="4"/>
       <c r="I350" s="2"/>
       <c r="J350" s="2"/>
     </row>
@@ -7355,7 +6997,6 @@
       <c r="E351" s="2">
         <v>56.5</v>
       </c>
-      <c r="G351" s="4"/>
       <c r="I351" s="2"/>
       <c r="J351" s="2"/>
     </row>
@@ -7375,7 +7016,6 @@
       <c r="E352" s="2">
         <v>63.5</v>
       </c>
-      <c r="G352" s="4"/>
       <c r="I352" s="2"/>
       <c r="J352" s="2"/>
     </row>
@@ -7395,7 +7035,6 @@
       <c r="E353" s="2">
         <v>83.0</v>
       </c>
-      <c r="G353" s="4"/>
       <c r="I353" s="2"/>
       <c r="J353" s="2"/>
     </row>
@@ -7415,7 +7054,6 @@
       <c r="E354" s="2">
         <v>127.0</v>
       </c>
-      <c r="G354" s="4"/>
       <c r="I354" s="2"/>
       <c r="J354" s="2"/>
     </row>
@@ -7435,7 +7073,6 @@
       <c r="E355" s="2">
         <v>159.0</v>
       </c>
-      <c r="G355" s="4"/>
       <c r="I355" s="2"/>
       <c r="J355" s="2"/>
     </row>
@@ -7455,7 +7092,6 @@
       <c r="E356" s="2">
         <v>238.0</v>
       </c>
-      <c r="G356" s="4"/>
       <c r="I356" s="2"/>
       <c r="J356" s="2"/>
     </row>
@@ -7475,7 +7111,6 @@
       <c r="E357" s="2">
         <v>246.0</v>
       </c>
-      <c r="G357" s="4"/>
       <c r="I357" s="2"/>
       <c r="J357" s="2"/>
     </row>
@@ -7495,7 +7130,6 @@
       <c r="E358" s="2">
         <v>57.0</v>
       </c>
-      <c r="G358" s="4"/>
       <c r="I358" s="2"/>
       <c r="J358" s="2"/>
     </row>
@@ -7515,7 +7149,6 @@
       <c r="E359" s="2">
         <v>64.5</v>
       </c>
-      <c r="G359" s="4"/>
       <c r="I359" s="2"/>
       <c r="J359" s="2"/>
     </row>
@@ -7535,7 +7168,6 @@
       <c r="E360" s="2">
         <v>84.0</v>
       </c>
-      <c r="G360" s="4"/>
       <c r="I360" s="2"/>
       <c r="J360" s="2"/>
     </row>
@@ -7555,7 +7187,6 @@
       <c r="E361" s="2">
         <v>129.0</v>
       </c>
-      <c r="G361" s="4"/>
       <c r="I361" s="2"/>
       <c r="J361" s="2"/>
     </row>
@@ -7575,7 +7206,6 @@
       <c r="E362" s="2">
         <v>160.0</v>
       </c>
-      <c r="G362" s="4"/>
       <c r="I362" s="2"/>
       <c r="J362" s="2"/>
     </row>
@@ -7595,7 +7225,6 @@
       <c r="E363" s="2">
         <v>240.0</v>
       </c>
-      <c r="G363" s="4"/>
       <c r="I363" s="2"/>
       <c r="J363" s="2"/>
     </row>
@@ -7615,7 +7244,6 @@
       <c r="E364" s="2">
         <v>249.0</v>
       </c>
-      <c r="G364" s="4"/>
       <c r="I364" s="2"/>
       <c r="J364" s="2"/>
     </row>
@@ -7635,7 +7263,6 @@
       <c r="E365" s="2">
         <v>59.0</v>
       </c>
-      <c r="G365" s="4"/>
       <c r="I365" s="2"/>
       <c r="J365" s="2"/>
     </row>
@@ -7655,7 +7282,6 @@
       <c r="E366" s="2">
         <v>65.5</v>
       </c>
-      <c r="G366" s="4"/>
       <c r="I366" s="2"/>
       <c r="J366" s="2"/>
     </row>
@@ -7675,7 +7301,6 @@
       <c r="E367" s="2">
         <v>86.5</v>
       </c>
-      <c r="G367" s="4"/>
       <c r="I367" s="2"/>
       <c r="J367" s="2"/>
     </row>
@@ -7692,10 +7317,9 @@
       <c r="D368" s="3">
         <v>4.0</v>
       </c>
-      <c r="E368" s="2">
+      <c r="E368" s="4">
         <v>134.0</v>
       </c>
-      <c r="G368" s="4"/>
       <c r="I368" s="2"/>
       <c r="J368" s="2"/>
     </row>
@@ -7715,7 +7339,6 @@
       <c r="E369" s="2">
         <v>170.0</v>
       </c>
-      <c r="G369" s="4"/>
       <c r="I369" s="2"/>
       <c r="J369" s="2"/>
     </row>
@@ -7735,7 +7358,6 @@
       <c r="E370" s="2">
         <v>249.0</v>
       </c>
-      <c r="G370" s="4"/>
       <c r="I370" s="2"/>
       <c r="J370" s="2"/>
     </row>
@@ -7755,7 +7377,6 @@
       <c r="E371" s="2">
         <v>261.0</v>
       </c>
-      <c r="G371" s="4"/>
       <c r="I371" s="2"/>
       <c r="J371" s="2"/>
     </row>
@@ -7775,7 +7396,6 @@
       <c r="E372" s="2">
         <v>61.0</v>
       </c>
-      <c r="G372" s="4"/>
       <c r="I372" s="2"/>
       <c r="J372" s="2"/>
     </row>
@@ -7795,7 +7415,6 @@
       <c r="E373" s="2">
         <v>66.5</v>
       </c>
-      <c r="G373" s="4"/>
       <c r="I373" s="2"/>
       <c r="J373" s="2"/>
     </row>
@@ -7815,7 +7434,6 @@
       <c r="E374" s="2">
         <v>88.5</v>
       </c>
-      <c r="G374" s="4"/>
       <c r="I374" s="2"/>
       <c r="J374" s="2"/>
     </row>
@@ -7835,7 +7453,6 @@
       <c r="E375" s="2">
         <v>139.0</v>
       </c>
-      <c r="G375" s="4"/>
       <c r="I375" s="2"/>
       <c r="J375" s="2"/>
     </row>
@@ -7855,7 +7472,6 @@
       <c r="E376" s="2">
         <v>175.0</v>
       </c>
-      <c r="G376" s="4"/>
       <c r="I376" s="2"/>
       <c r="J376" s="2"/>
     </row>
@@ -7872,10 +7488,9 @@
       <c r="D377" s="3">
         <v>5.0</v>
       </c>
-      <c r="E377" s="5">
-        <v>259.0</v>
-      </c>
-      <c r="G377" s="4"/>
+      <c r="E377" s="2">
+        <v>269.0</v>
+      </c>
       <c r="I377" s="2"/>
       <c r="J377" s="2"/>
     </row>
@@ -7895,7 +7510,6 @@
       <c r="E378" s="2">
         <v>265.0</v>
       </c>
-      <c r="G378" s="4"/>
       <c r="I378" s="2"/>
       <c r="J378" s="2"/>
     </row>
@@ -7915,7 +7529,6 @@
       <c r="E379" s="2">
         <v>61.5</v>
       </c>
-      <c r="G379" s="4"/>
       <c r="I379" s="2"/>
       <c r="J379" s="2"/>
     </row>
@@ -7935,7 +7548,6 @@
       <c r="E380" s="2">
         <v>68.0</v>
       </c>
-      <c r="G380" s="4"/>
       <c r="I380" s="2"/>
       <c r="J380" s="2"/>
     </row>
@@ -7955,7 +7567,6 @@
       <c r="E381" s="2">
         <v>89.5</v>
       </c>
-      <c r="G381" s="4"/>
       <c r="I381" s="2"/>
       <c r="J381" s="2"/>
     </row>
@@ -7975,7 +7586,6 @@
       <c r="E382" s="2">
         <v>139.5</v>
       </c>
-      <c r="G382" s="4"/>
       <c r="I382" s="2"/>
       <c r="J382" s="2"/>
     </row>
@@ -7995,7 +7605,6 @@
       <c r="E383" s="2">
         <v>176.0</v>
       </c>
-      <c r="G383" s="4"/>
       <c r="I383" s="2"/>
       <c r="J383" s="2"/>
     </row>
@@ -8015,7 +7624,6 @@
       <c r="E384" s="2">
         <v>264.0</v>
       </c>
-      <c r="G384" s="4"/>
       <c r="I384" s="2"/>
       <c r="J384" s="2"/>
     </row>
@@ -8035,7 +7643,6 @@
       <c r="E385" s="2">
         <v>275.0</v>
       </c>
-      <c r="G385" s="4"/>
       <c r="I385" s="2"/>
       <c r="J385" s="2"/>
     </row>
@@ -8055,7 +7662,6 @@
       <c r="E386" s="2">
         <v>60.0</v>
       </c>
-      <c r="G386" s="4"/>
       <c r="I386" s="2"/>
       <c r="J386" s="2"/>
     </row>
@@ -8075,7 +7681,6 @@
       <c r="E387" s="2">
         <v>72.0</v>
       </c>
-      <c r="G387" s="4"/>
       <c r="I387" s="2"/>
       <c r="J387" s="2"/>
     </row>
@@ -8095,7 +7700,6 @@
       <c r="E388" s="2">
         <v>89.0</v>
       </c>
-      <c r="G388" s="4"/>
       <c r="I388" s="2"/>
       <c r="J388" s="2"/>
     </row>
@@ -8115,7 +7719,6 @@
       <c r="E389" s="2">
         <v>125.0</v>
       </c>
-      <c r="G389" s="4"/>
       <c r="I389" s="2"/>
       <c r="J389" s="2"/>
     </row>
@@ -8135,7 +7738,6 @@
       <c r="E390" s="2">
         <v>189.0</v>
       </c>
-      <c r="G390" s="4"/>
       <c r="I390" s="2"/>
       <c r="J390" s="2"/>
     </row>
@@ -8155,7 +7757,6 @@
       <c r="E391" s="2">
         <v>62.0</v>
       </c>
-      <c r="G391" s="4"/>
       <c r="I391" s="2"/>
       <c r="J391" s="2"/>
     </row>
@@ -8175,7 +7776,6 @@
       <c r="E392" s="2">
         <v>73.0</v>
       </c>
-      <c r="G392" s="4"/>
       <c r="I392" s="2"/>
       <c r="J392" s="2"/>
     </row>
@@ -8195,7 +7795,6 @@
       <c r="E393" s="2">
         <v>95.0</v>
       </c>
-      <c r="G393" s="4"/>
       <c r="I393" s="2"/>
       <c r="J393" s="2"/>
     </row>
@@ -8215,7 +7814,6 @@
       <c r="E394" s="2">
         <v>129.0</v>
       </c>
-      <c r="G394" s="4"/>
       <c r="I394" s="2"/>
       <c r="J394" s="2"/>
     </row>
@@ -8235,7 +7833,6 @@
       <c r="E395" s="2">
         <v>199.0</v>
       </c>
-      <c r="G395" s="4"/>
       <c r="I395" s="2"/>
       <c r="J395" s="2"/>
     </row>
@@ -8255,7 +7852,6 @@
       <c r="E396" s="2">
         <v>63.0</v>
       </c>
-      <c r="G396" s="4"/>
       <c r="I396" s="2"/>
       <c r="J396" s="2"/>
     </row>
@@ -8275,7 +7871,6 @@
       <c r="E397" s="2">
         <v>75.0</v>
       </c>
-      <c r="G397" s="4"/>
       <c r="I397" s="2"/>
       <c r="J397" s="2"/>
     </row>
@@ -8295,7 +7890,6 @@
       <c r="E398" s="2">
         <v>98.0</v>
       </c>
-      <c r="G398" s="4"/>
       <c r="I398" s="2"/>
       <c r="J398" s="2"/>
     </row>
@@ -8315,7 +7909,6 @@
       <c r="E399" s="2">
         <v>135.0</v>
       </c>
-      <c r="G399" s="4"/>
       <c r="I399" s="2"/>
       <c r="J399" s="2"/>
     </row>
@@ -8335,7 +7928,6 @@
       <c r="E400" s="2">
         <v>205.0</v>
       </c>
-      <c r="G400" s="4"/>
       <c r="I400" s="2"/>
       <c r="J400" s="2"/>
     </row>
@@ -8355,7 +7947,6 @@
       <c r="E401" s="2">
         <v>65.0</v>
       </c>
-      <c r="G401" s="4"/>
       <c r="I401" s="2"/>
       <c r="J401" s="2"/>
     </row>
@@ -8375,7 +7966,6 @@
       <c r="E402" s="2">
         <v>76.0</v>
       </c>
-      <c r="G402" s="4"/>
       <c r="I402" s="2"/>
       <c r="J402" s="2"/>
     </row>
@@ -8395,7 +7985,6 @@
       <c r="E403" s="2">
         <v>99.0</v>
       </c>
-      <c r="G403" s="4"/>
       <c r="I403" s="2"/>
       <c r="J403" s="2"/>
     </row>
@@ -8415,7 +8004,6 @@
       <c r="E404" s="2">
         <v>139.0</v>
       </c>
-      <c r="G404" s="4"/>
       <c r="I404" s="2"/>
       <c r="J404" s="2"/>
     </row>
@@ -8435,7 +8023,6 @@
       <c r="E405" s="2">
         <v>209.0</v>
       </c>
-      <c r="G405" s="4"/>
       <c r="I405" s="2"/>
       <c r="J405" s="2"/>
     </row>
@@ -8455,7 +8042,6 @@
       <c r="E406" s="2">
         <v>66.0</v>
       </c>
-      <c r="G406" s="4"/>
       <c r="I406" s="2"/>
       <c r="J406" s="2"/>
     </row>
@@ -8475,7 +8061,6 @@
       <c r="E407" s="2">
         <v>79.0</v>
       </c>
-      <c r="G407" s="4"/>
       <c r="I407" s="2"/>
       <c r="J407" s="2"/>
     </row>
@@ -8495,7 +8080,6 @@
       <c r="E408" s="2">
         <v>105.0</v>
       </c>
-      <c r="G408" s="4"/>
       <c r="I408" s="2"/>
       <c r="J408" s="2"/>
     </row>
@@ -8515,7 +8099,6 @@
       <c r="E409" s="2">
         <v>139.0</v>
       </c>
-      <c r="G409" s="4"/>
       <c r="I409" s="2"/>
       <c r="J409" s="2"/>
     </row>
@@ -8535,7 +8118,6 @@
       <c r="E410" s="2">
         <v>219.0</v>
       </c>
-      <c r="G410" s="4"/>
       <c r="I410" s="2"/>
       <c r="J410" s="2"/>
     </row>
@@ -8555,7 +8137,6 @@
       <c r="E411" s="2">
         <v>67.0</v>
       </c>
-      <c r="G411" s="4"/>
       <c r="I411" s="2"/>
       <c r="J411" s="2"/>
     </row>
@@ -8575,7 +8156,6 @@
       <c r="E412" s="2">
         <v>80.0</v>
       </c>
-      <c r="G412" s="4"/>
       <c r="I412" s="2"/>
       <c r="J412" s="2"/>
     </row>
@@ -8595,7 +8175,6 @@
       <c r="E413" s="2">
         <v>110.0</v>
       </c>
-      <c r="G413" s="4"/>
       <c r="I413" s="2"/>
       <c r="J413" s="2"/>
     </row>
@@ -8615,7 +8194,6 @@
       <c r="E414" s="2">
         <v>145.0</v>
       </c>
-      <c r="G414" s="4"/>
       <c r="I414" s="2"/>
       <c r="J414" s="2"/>
     </row>
@@ -8635,7 +8213,6 @@
       <c r="E415" s="2">
         <v>225.0</v>
       </c>
-      <c r="G415" s="4"/>
       <c r="I415" s="2"/>
       <c r="J415" s="2"/>
     </row>
